--- a/data/vendor-search/results_all_garden.xlsx
+++ b/data/vendor-search/results_all_garden.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>cpe:2.3:o:rainmachine:mini-8_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:rainmachine:mini-8:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
           <t>cpe:2.3:o:rainmachine:mini-8_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:rainmachine:mini-8:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,6 +572,11 @@
           <t>cpe:2.3:a:rainmachine:rainmachine_web_application:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,6 +612,11 @@
           <t>cpe:2.3:a:rainmachine:rainmachine_web_application:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -627,6 +652,11 @@
           <t>cpe:2.3:o:rainmachine:mini-8_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:rainmachine:mini-8:-:*:*:*:*:*:*:*|cpe:2.3:o:rainmachine:touch_hd_12_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:rainmachine:touch_hd_12:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +692,11 @@
           <t>cpe:2.3:a:rainmachine:rainmachine_web_application:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rainmachine</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -697,6 +732,11 @@
           <t>cpe:2.3:o:ecowitt:gw1100_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:ecowitt:gw1100:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ecowitt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -732,6 +772,11 @@
           <t>cpe:2.3:o:yarbo:lawn_mower_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower:-:*:*:*:*:*:*:*|cpe:2.3:o:yarbo:lawn_mower_pro_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower_pro:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>yarbo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -767,6 +812,11 @@
           <t>cpe:2.3:o:yarbo:lawn_mower_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower:-:*:*:*:*:*:*:*|cpe:2.3:o:yarbo:lawn_mower_pro_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower_pro:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yarbo</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,6 +852,11 @@
           <t>cpe:2.3:o:yarbo:lawn_mower_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower:-:*:*:*:*:*:*:*|cpe:2.3:o:yarbo:lawn_mower_pro_firmware:2.3.9:*:*:*:*:*:*:*|cpe:2.3:h:yarbo:lawn_mower_pro:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>yarbo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -833,6 +888,11 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>yarbo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -864,6 +924,11 @@
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>yarbo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
